--- a/evergreen_yp/data-collection/modbus_reader/ups/modbus_config/FT-PI01_ups_modbus_address.xlsx
+++ b/evergreen_yp/data-collection/modbus_reader/ups/modbus_config/FT-PI01_ups_modbus_address.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chingjenchen/Dropbox/FEMC/Python Program/auto-modbus-reader/field_modbus_config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chingjenchen/Dropbox/FEMC/Field Deploy/field-deploy/evergreen_yp/data-collection/modbus_reader/ups/modbus_config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535078AC-561D-4744-AB42-A3D85B76C96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C10AF49-D324-9A4E-BCE2-B5E48365B672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connection Config" sheetId="1" r:id="rId1"/>
@@ -65,9 +65,6 @@
     <t>ups</t>
   </si>
   <si>
-    <t>192.168.100.170</t>
-  </si>
-  <si>
     <t>502</t>
   </si>
   <si>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>65</t>
+  </si>
+  <si>
+    <t>192.168.100.110</t>
   </si>
 </sst>
 </file>
@@ -563,22 +563,22 @@
         <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -619,695 +619,695 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="N8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="N9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
